--- a/examples/outputs/barnes-maze-sample-results.xlsx
+++ b/examples/outputs/barnes-maze-sample-results.xlsx
@@ -194,7 +194,7 @@
     <t>analyzed_at</t>
   </si>
   <si>
-    <t>2026-08-31T20:30:48.405Z</t>
+    <t>2026-08-31T21:53:33.193Z</t>
   </si>
   <si>
     <t>sampling</t>
@@ -828,7 +828,7 @@
         <v>1253.7852830989489</v>
       </c>
       <c r="L2">
-        <v>6.980987099660074</v>
+        <v>6.980987099660072</v>
       </c>
       <c r="M2">
         <v>82.33333333333333</v>
@@ -872,7 +872,7 @@
         <v>217.57802025036344</v>
       </c>
       <c r="L3">
-        <v>4.405959316029171</v>
+        <v>4.4059593160291755</v>
       </c>
       <c r="M3">
         <v>18.685333333333332</v>
@@ -916,7 +916,7 @@
         <v>105.52461561712477</v>
       </c>
       <c r="L4">
-        <v>4.198592133307352</v>
+        <v>4.1985921333073515</v>
       </c>
       <c r="M4">
         <v>25.133333333333333</v>
